--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/MstBondCreditRating.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/MstBondCreditRating.xlsx
@@ -3,6 +3,11 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="153222"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\dev0401-huaxia\tams\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20460" windowHeight="7680"/>
   </bookViews>
@@ -608,9 +613,13 @@
     <row r="2" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="A2:A1048576">
       <formula1>"导出,新增,修改,删除"</formula1>
+    </dataValidation>
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="正确格式为1900-01-01" sqref="D2:D1048576">
+      <formula1>1</formula1>
+      <formula2>2958465</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
